--- a/output/提出用_工賃実績報告.xlsx
+++ b/output/提出用_工賃実績報告.xlsx
@@ -3378,10 +3378,10 @@
         <v>20</v>
       </c>
       <c r="C8" s="63" t="n">
-        <v>25000</v>
+        <v>784000</v>
       </c>
       <c r="D8" s="63" t="n">
-        <v>9</v>
+        <v>720</v>
       </c>
       <c r="E8" s="63" t="n">
         <v>240</v>
